--- a/reference/origins/product info/Flower Final pt2 Product List for WA.xlsx
+++ b/reference/origins/product info/Flower Final pt2 Product List for WA.xlsx
@@ -3983,7 +3983,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Constellation Cannabis</t>
+          <t>Constellation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">

--- a/reference/origins/product info/Flower Final pt2 Product List for WA.xlsx
+++ b/reference/origins/product info/Flower Final pt2 Product List for WA.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flower Catalog" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Description Sources" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Flower Catalog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Description Sources" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="20" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Nerolidol</t>
         </is>
       </c>
       <c r="M4" s="20" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="N7" s="20" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Linalool</t>
         </is>
       </c>
       <c r="O7" s="20" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="N8" s="20" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Linalool</t>
         </is>
       </c>
       <c r="O8" s="20" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="L11" s="20" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Humulene</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="N12" s="20" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Linalool</t>
         </is>
       </c>
       <c r="O12" s="20" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Ocimene</t>
         </is>
       </c>
       <c r="M13" s="20" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Bisabolol</t>
         </is>
       </c>
       <c r="O15" s="20" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
+          <t>Caryophyllene</t>
+        </is>
+      </c>
+      <c r="M17" s="20" t="inlineStr">
+        <is>
           <t>Limonene</t>
-        </is>
-      </c>
-      <c r="M17" s="20" t="inlineStr">
-        <is>
-          <t>Caryophyllene</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -1498,17 +1498,17 @@
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
+          <t>Limonene</t>
+        </is>
+      </c>
+      <c r="M18" s="20" t="inlineStr">
+        <is>
           <t>Terpinolene</t>
         </is>
       </c>
-      <c r="M18" s="20" t="inlineStr">
-        <is>
-          <t>Caryophyllene</t>
-        </is>
-      </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Caryophyllene</t>
         </is>
       </c>
       <c r="O18" s="20" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="M19" s="20" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Ocimene</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Caryophyllene</t>
         </is>
       </c>
       <c r="O19" s="20" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
-          <t>Pinene</t>
+          <t>Linalool</t>
         </is>
       </c>
       <c r="O20" s="20" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Limonene</t>
         </is>
       </c>
       <c r="M23" s="20" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Myrcene</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Caryophyllene</t>
         </is>
       </c>
       <c r="O23" s="20" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
-          <t>Pinene</t>
+          <t>Limonene</t>
         </is>
       </c>
       <c r="O24" s="20" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Linalool</t>
         </is>
       </c>
       <c r="O27" s="20" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="M29" s="33" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Bisabolol</t>
         </is>
       </c>
       <c r="N29" s="33" t="inlineStr">
@@ -2317,17 +2317,17 @@
       </c>
       <c r="L31" s="33" t="inlineStr">
         <is>
+          <t>Humulene</t>
+        </is>
+      </c>
+      <c r="M31" s="33" t="inlineStr">
+        <is>
           <t>Myrcene</t>
         </is>
       </c>
-      <c r="M31" s="33" t="inlineStr">
-        <is>
-          <t>Caryophyllene</t>
-        </is>
-      </c>
       <c r="N31" s="33" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Pinene</t>
         </is>
       </c>
       <c r="O31" s="33" t="inlineStr">
@@ -2443,17 +2443,17 @@
       </c>
       <c r="L33" s="33" t="inlineStr">
         <is>
+          <t>Terpinolene</t>
+        </is>
+      </c>
+      <c r="M33" s="33" t="inlineStr">
+        <is>
+          <t>Pinene</t>
+        </is>
+      </c>
+      <c r="N33" s="33" t="inlineStr">
+        <is>
           <t>Myrcene</t>
-        </is>
-      </c>
-      <c r="M33" s="33" t="inlineStr">
-        <is>
-          <t>Pinene</t>
-        </is>
-      </c>
-      <c r="N33" s="33" t="inlineStr">
-        <is>
-          <t>Caryophyllene</t>
         </is>
       </c>
       <c r="O33" s="33" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="M36" s="20" t="inlineStr">
         <is>
+          <t>Ocimene</t>
+        </is>
+      </c>
+      <c r="N36" s="20" t="inlineStr">
+        <is>
           <t>Myrcene</t>
-        </is>
-      </c>
-      <c r="N36" s="20" t="inlineStr">
-        <is>
-          <t>Pinene</t>
         </is>
       </c>
       <c r="O36" s="20" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L39" s="20" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Limonene</t>
         </is>
       </c>
       <c r="M39" s="20" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Caryophyllene</t>
         </is>
       </c>
       <c r="N39" s="20" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Linalool</t>
         </is>
       </c>
       <c r="O41" s="20" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="L42" s="20" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Limonene</t>
         </is>
       </c>
       <c r="M42" s="20" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Caryophyllene</t>
         </is>
       </c>
       <c r="N42" s="20" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="L44" s="20" t="inlineStr">
         <is>
+          <t>Limonene</t>
+        </is>
+      </c>
+      <c r="M44" s="20" t="inlineStr">
+        <is>
           <t>Myrcene</t>
-        </is>
-      </c>
-      <c r="M44" s="20" t="inlineStr">
-        <is>
-          <t>Pinene</t>
         </is>
       </c>
       <c r="N44" s="20" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="L51" s="20" t="inlineStr">
         <is>
+          <t>Limonene</t>
+        </is>
+      </c>
+      <c r="M51" s="20" t="inlineStr">
+        <is>
           <t>Terpinolene</t>
         </is>
       </c>
-      <c r="M51" s="20" t="inlineStr">
+      <c r="N51" s="20" t="inlineStr">
         <is>
           <t>Myrcene</t>
-        </is>
-      </c>
-      <c r="N51" s="20" t="inlineStr">
-        <is>
-          <t>Caryophyllene</t>
         </is>
       </c>
       <c r="O51" s="20" t="inlineStr">
@@ -3699,17 +3699,17 @@
       </c>
       <c r="L53" s="20" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Myrcene</t>
         </is>
       </c>
       <c r="M53" s="20" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Caryophyllene</t>
         </is>
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Linalool</t>
         </is>
       </c>
       <c r="O53" s="20" t="inlineStr">
